--- a/naver-place-crawler/results_health/서초_PT.xlsx
+++ b/naver-place-crawler/results_health/서초_PT.xlsx
@@ -417,17 +417,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
     <col width="27" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="46" customWidth="1" min="7" max="7"/>
+    <col width="38" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -591,12 +591,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -624,10 +624,10 @@
         <v>220</v>
       </c>
       <c r="Q2" t="n">
-        <v>623</v>
+        <v>616</v>
       </c>
       <c r="R2" t="n">
-        <v>843</v>
+        <v>836</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="Q3" t="n">
-        <v>542</v>
+        <v>548</v>
       </c>
       <c r="R3" t="n">
-        <v>644</v>
+        <v>651</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1970</v>
+        <v>1971</v>
       </c>
       <c r="Q4" t="n">
         <v>1603</v>
       </c>
       <c r="R4" t="n">
-        <v>3573</v>
+        <v>3574</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -910,10 +910,10 @@
         <v>233</v>
       </c>
       <c r="Q5" t="n">
-        <v>1554</v>
+        <v>1555</v>
       </c>
       <c r="R5" t="n">
-        <v>1787</v>
+        <v>1788</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -944,25 +944,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>강남역 PT 바디스펙트럼</t>
+          <t>MN휘트니스 헬스 PT 강남역점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>bodyspectrum@naver.com</t>
+          <t>mnfitness1@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0507-1361-0000</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>서울특별시 서초구 강남대로53길 7 애니타워 301호 강남역 PT 바디스펙트럼</t>
+          <t>서울특별시 서초구 사임당로 174 강남미래타워 지하1층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://bodyspectrum.co.kr/</t>
+          <t>http://www.mnkorea.kr</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -972,7 +976,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -988,7 +992,7 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -997,13 +1001,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>117</v>
+        <v>962</v>
       </c>
       <c r="Q6" t="n">
-        <v>834</v>
+        <v>997</v>
       </c>
       <c r="R6" t="n">
-        <v>951</v>
+        <v>1959</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,12 +1016,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1084545069</t>
+          <t>36615340</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1084545069</t>
+          <t>https://m.place.naver.com/place/36615340</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1034,29 +1038,25 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MN휘트니스 헬스 PT 강남역점</t>
+          <t>강남역 PT 바디스펙트럼</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>mnfitness1@naver.com</t>
+          <t>bodyspectrum@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0507-1361-0000</t>
-        </is>
-      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>서울특별시 서초구 사임당로 174 강남미래타워 지하1층</t>
+          <t>서울특별시 서초구 강남대로53길 7 애니타워 301호 강남역 PT 바디스펙트럼</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>http://www.mnkorea.kr</t>
+          <t>https://bodyspectrum.co.kr/</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1082,7 +1082,7 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1091,13 +1091,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>962</v>
+        <v>117</v>
       </c>
       <c r="Q7" t="n">
-        <v>997</v>
+        <v>838</v>
       </c>
       <c r="R7" t="n">
-        <v>1959</v>
+        <v>955</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>36615340</t>
+          <t>1084545069</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36615340</t>
+          <t>https://m.place.naver.com/place/1084545069</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1222,29 +1222,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>짐에브리원PT 방배이수점</t>
+          <t>리프레쉬클럽 PT 반포래미안점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>speedangel26@naver.com</t>
+          <t>refreshbanpo@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1362-1331</t>
+          <t>0507-1402-8731</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울특별시 서초구 서초대로 3-4 디오슈페리움1차 413-1호</t>
+          <t>서울특별시 서초구 반포대로 287 래미안퍼스티지중심상가 3층 327호, 328호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/speedangel26/222432679411</t>
+          <t>https://blog.naver.com/refreshbanpo</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1279,13 +1279,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>277</v>
+        <v>303</v>
       </c>
       <c r="Q9" t="n">
         <v>352</v>
       </c>
       <c r="R9" t="n">
-        <v>629</v>
+        <v>655</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,12 +1294,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1403416985</t>
+          <t>20451191</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1403416985</t>
+          <t>https://m.place.naver.com/place/20451191</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1405,92 +1405,190 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>크레이지독스짐</t>
+          <t>트리니티 PT Pilates LAB</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>bodyartist7@naver.com</t>
+          <t>trinity_pt@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1314-7087</t>
+          <t>0507-2097-3213</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
+          <t>서울 서초구 서초대로48길 107 6층</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/trinity_pt</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wg58axz</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>73</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>95</v>
+      </c>
+      <c r="R11" t="n">
+        <v>168</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>1015744638</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1015744638</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>크레이지독스짐</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>bodyartist7@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1314-7087</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
           <t>서울특별시 서초구 효령로31길 10 지하 1층</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>https://blog.naver.com/bodyartist7</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P11" t="n">
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
         <v>783</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="Q12" t="n">
         <v>398</v>
       </c>
-      <c r="R11" t="n">
+      <c r="R12" t="n">
         <v>1181</v>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
         <is>
           <t>1659233801</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/1659233801</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>2026-04-14</t>
         </is>

--- a/naver-place-crawler/results_health/서초_PT.xlsx
+++ b/naver-place-crawler/results_health/서초_PT.xlsx
@@ -421,13 +421,13 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
     <col width="27" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="46" customWidth="1" min="7" max="7"/>
-    <col width="38" customWidth="1" min="8" max="8"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>파프짐 서초점</t>
+          <t>고마워휘트니스 교대PT</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>finest2010@naver.com</t>
+          <t>gmw1253@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1362-7051</t>
+          <t>0507-1455-1284</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>서울특별시 서초구 효령로77길 14 1층 PAFGYM</t>
+          <t>서울특별시 서초구 서초중앙로 166 B1 고마워 휘트니스</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://pafgym.com</t>
+          <t>https://blog.naver.com/gmw1253/223435367519</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,7 +596,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>220</v>
+        <v>344</v>
       </c>
       <c r="Q2" t="n">
-        <v>616</v>
+        <v>1600</v>
       </c>
       <c r="R2" t="n">
-        <v>836</v>
+        <v>1944</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,17 +636,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1515526804</t>
+          <t>11875969</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1515526804</t>
+          <t>https://m.place.naver.com/place/11875969</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="Q3" t="n">
-        <v>548</v>
+        <v>583</v>
       </c>
       <c r="R3" t="n">
-        <v>651</v>
+        <v>693</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1971</v>
+        <v>1972</v>
       </c>
       <c r="Q4" t="n">
-        <v>1603</v>
+        <v>1606</v>
       </c>
       <c r="R4" t="n">
-        <v>3574</v>
+        <v>3578</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -850,29 +850,25 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>바른핏PT필라테스</t>
+          <t>아고라피트니스 헬스&amp;PT 강남역점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>bareunfit2024@naver.com</t>
+          <t>agorablog@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0507-1384-5988</t>
-        </is>
-      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>서울특별시 서초구 서초중앙로24길 17 지하1층 바른핏PT필라테스</t>
+          <t>서울특별시 서초구 서초대로78길 38 5층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bareunfit2024</t>
+          <t>https://blog.naver.com/agorablog</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -907,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>233</v>
+        <v>318</v>
       </c>
       <c r="Q5" t="n">
-        <v>1555</v>
+        <v>1394</v>
       </c>
       <c r="R5" t="n">
-        <v>1788</v>
+        <v>1712</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -922,17 +918,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1580973564</t>
+          <t>1034599129</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1580973564</t>
+          <t>https://m.place.naver.com/place/1034599129</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1001,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>962</v>
+        <v>964</v>
       </c>
       <c r="Q6" t="n">
         <v>997</v>
       </c>
       <c r="R6" t="n">
-        <v>1959</v>
+        <v>1961</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1026,7 +1022,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1061,17 +1057,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1082,7 +1078,7 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1094,10 +1090,10 @@
         <v>117</v>
       </c>
       <c r="Q7" t="n">
-        <v>838</v>
+        <v>849</v>
       </c>
       <c r="R7" t="n">
-        <v>955</v>
+        <v>966</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1116,7 +1112,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1128,34 +1124,34 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>데이원 피트니스 교대PT</t>
+          <t>바른핏PT필라테스</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>day1fitness@naver.com</t>
+          <t>bareunfit2024@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1373-1906</t>
+          <t>0507-1384-5988</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울특별시 서초구 서초대로53길 10 지하1층</t>
+          <t>서울특별시 서초구 서초중앙로24길 17 지하1층 바른핏PT필라테스</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_fxbuCn</t>
+          <t>https://blog.naver.com/bareunfit2024</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1165,7 +1161,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1176,7 +1172,7 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1185,13 +1181,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>275</v>
+        <v>233</v>
       </c>
       <c r="Q8" t="n">
-        <v>1590</v>
+        <v>1572</v>
       </c>
       <c r="R8" t="n">
-        <v>1865</v>
+        <v>1805</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,17 +1196,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1732770907</t>
+          <t>1580973564</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1732770907</t>
+          <t>https://m.place.naver.com/place/1580973564</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1282,10 +1278,10 @@
         <v>303</v>
       </c>
       <c r="Q9" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="R9" t="n">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1304,46 +1300,46 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>윈핏 PT 스튜디오</t>
+          <t>휴메이크휘트니스 강남점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>winfit_official@naver.com</t>
+          <t>humake001@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>02-533-5503</t>
+          <t>0507-1432-0174</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울특별시 서초구 서초대로27길 51 지하1층</t>
+          <t>서울특별시 서초구 강남대로 327 대륭서초타워 지하2층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_ejvnG/chat</t>
+          <t>http://www.instagram.com/humakefitness_gn</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1364,7 +1360,7 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1373,13 +1369,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>64</v>
+        <v>1017</v>
       </c>
       <c r="Q10" t="n">
-        <v>37</v>
+        <v>1271</v>
       </c>
       <c r="R10" t="n">
-        <v>101</v>
+        <v>2288</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,17 +1384,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1161388796</t>
+          <t>20077206</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1161388796</t>
+          <t>https://m.place.naver.com/place/20077206</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1410,34 +1406,34 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>트리니티 PT Pilates LAB</t>
+          <t>윈핏 PT 스튜디오</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>trinity_pt@naver.com</t>
+          <t>winfit_official@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-2097-3213</t>
+          <t>02-533-5503</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울 서초구 서초대로48길 107 6층</t>
+          <t>서울특별시 서초구 서초대로27길 51 지하1층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/trinity_pt</t>
+          <t>http://pf.kakao.com/_ejvnG/chat</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1447,22 +1443,18 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wg58axz</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1471,13 +1463,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="Q11" t="n">
-        <v>95</v>
+        <v>36</v>
       </c>
       <c r="R11" t="n">
-        <v>168</v>
+        <v>101</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1486,17 +1478,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1015744638</t>
+          <t>1161388796</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1015744638</t>
+          <t>https://m.place.naver.com/place/1161388796</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1508,29 +1500,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>크레이지독스짐</t>
+          <t>휴메이크휘트니스 서초점</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>bodyartist7@naver.com</t>
+          <t>humakesc@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1314-7087</t>
+          <t>0507-1352-4800</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>서울특별시 서초구 효령로31길 10 지하 1층</t>
+          <t>서울특별시 서초구 반포대로 34 로얄빌딩 지하1층 휴메이크휘트니스 서초점</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bodyartist7</t>
+          <t>https://blog.naver.com/humakesc</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1565,13 +1557,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>783</v>
+        <v>770</v>
       </c>
       <c r="Q12" t="n">
-        <v>398</v>
+        <v>1004</v>
       </c>
       <c r="R12" t="n">
-        <v>1181</v>
+        <v>1774</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1580,17 +1572,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1659233801</t>
+          <t>32308075</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1659233801</t>
+          <t>https://m.place.naver.com/place/32308075</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/서초_PT.xlsx
+++ b/naver-place-crawler/results_health/서초_PT.xlsx
@@ -417,17 +417,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="46" customWidth="1" min="7" max="7"/>
-    <col width="45" customWidth="1" min="8" max="8"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="Q2" t="n">
-        <v>1600</v>
+        <v>1638</v>
       </c>
       <c r="R2" t="n">
-        <v>1944</v>
+        <v>1980</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -646,7 +646,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Q3" t="n">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="R3" t="n">
-        <v>693</v>
+        <v>699</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -903,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q5" t="n">
-        <v>1394</v>
+        <v>1397</v>
       </c>
       <c r="R5" t="n">
-        <v>1712</v>
+        <v>1716</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -928,7 +928,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1000,10 +1000,10 @@
         <v>964</v>
       </c>
       <c r="Q6" t="n">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="R6" t="n">
-        <v>1961</v>
+        <v>1962</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1057,17 +1057,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1078,7 +1078,7 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1087,13 +1087,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="Q7" t="n">
-        <v>849</v>
+        <v>852</v>
       </c>
       <c r="R7" t="n">
-        <v>966</v>
+        <v>968</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1124,29 +1124,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>바른핏PT필라테스</t>
+          <t>헬스보이짐 필라걸 신논현점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>bareunfit2024@naver.com</t>
+          <t>healthboy45@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1384-5988</t>
+          <t>0507-1364-7391</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울특별시 서초구 서초중앙로24길 17 지하1층 바른핏PT필라테스</t>
+          <t>서울특별시 서초구 사평대로56길 7 서초한일유앤아이주상복합 지하2층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bareunfit2024</t>
+          <t>https://blog.naver.com/healthboy45</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1181,13 +1181,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>233</v>
+        <v>1070</v>
       </c>
       <c r="Q8" t="n">
-        <v>1572</v>
+        <v>655</v>
       </c>
       <c r="R8" t="n">
-        <v>1805</v>
+        <v>1725</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1196,51 +1196,51 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1580973564</t>
+          <t>1810083742</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1580973564</t>
+          <t>https://m.place.naver.com/place/1810083742</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>리프레쉬클럽 PT 반포래미안점</t>
+          <t>휴메이크휘트니스 강남점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>refreshbanpo@naver.com</t>
+          <t>humake001@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1402-8731</t>
+          <t>0507-1432-0174</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울특별시 서초구 반포대로 287 래미안퍼스티지중심상가 3층 327호, 328호</t>
+          <t>서울특별시 서초구 강남대로 327 대륭서초타워 지하2층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/refreshbanpo</t>
+          <t>http://www.instagram.com/humakefitness_gn</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1275,13 +1275,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>303</v>
+        <v>1019</v>
       </c>
       <c r="Q9" t="n">
-        <v>353</v>
+        <v>1272</v>
       </c>
       <c r="R9" t="n">
-        <v>656</v>
+        <v>2291</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1290,51 +1290,51 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>20451191</t>
+          <t>20077206</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20451191</t>
+          <t>https://m.place.naver.com/place/20077206</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>휴메이크휘트니스 강남점</t>
+          <t>트리니티 PT Pilates LAB</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>humake001@naver.com</t>
+          <t>trinity_pt@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1432-0174</t>
+          <t>0507-2097-3213</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울특별시 서초구 강남대로 327 대륭서초타워 지하2층</t>
+          <t>서울 서초구 서초대로48길 107 6층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/humakefitness_gn</t>
+          <t>https://blog.naver.com/trinity_pt</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1349,15 +1349,19 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wg58axz</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1369,13 +1373,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1017</v>
+        <v>74</v>
       </c>
       <c r="Q10" t="n">
-        <v>1271</v>
+        <v>98</v>
       </c>
       <c r="R10" t="n">
-        <v>2288</v>
+        <v>172</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1384,56 +1388,56 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>20077206</t>
+          <t>1015744638</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20077206</t>
+          <t>https://m.place.naver.com/place/1015744638</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>윈핏 PT 스튜디오</t>
+          <t>크레이지독스짐</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>winfit_official@naver.com</t>
+          <t>bodyartist7@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>02-533-5503</t>
+          <t>0507-1314-7087</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울특별시 서초구 서초대로27길 51 지하1층</t>
+          <t>서울특별시 서초구 효령로31길 10 지하 1층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_ejvnG/chat</t>
+          <t>https://blog.naver.com/bodyartist7</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1443,7 +1447,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1454,7 +1458,7 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1463,13 +1467,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>65</v>
+        <v>789</v>
       </c>
       <c r="Q11" t="n">
-        <v>36</v>
+        <v>400</v>
       </c>
       <c r="R11" t="n">
-        <v>101</v>
+        <v>1189</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1478,51 +1482,51 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1161388796</t>
+          <t>1659233801</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1161388796</t>
+          <t>https://m.place.naver.com/place/1659233801</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>휴메이크휘트니스 서초점</t>
+          <t>피치짐PT&amp;필라테스 서초점</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>humakesc@naver.com</t>
+          <t>peachgym1@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1352-4800</t>
+          <t>0507-1363-0878</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>서울특별시 서초구 반포대로 34 로얄빌딩 지하1층 휴메이크휘트니스 서초점</t>
+          <t>서울특별시 서초구 명달로20길 21 1층 피치짐</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/humakesc</t>
+          <t>https://blog.naver.com/peachgym1</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1553,17 +1557,17 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>770</v>
+        <v>396</v>
       </c>
       <c r="Q12" t="n">
-        <v>1004</v>
+        <v>379</v>
       </c>
       <c r="R12" t="n">
-        <v>1774</v>
+        <v>775</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1572,17 +1576,107 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>32308075</t>
+          <t>1387134259</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/32308075</t>
+          <t>https://m.place.naver.com/place/1387134259</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>복싱,권투장</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>잽트레이닝 복싱 교대점</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>jab_training@naver.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>서울 서초구 서초중앙로22길 53 지하1층</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://cafe.naver.com/jabtraining?iframe_url=/MyCafeIntro.nhn%3Fclubid=31590001</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>140</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>4</v>
+      </c>
+      <c r="R13" t="n">
+        <v>144</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>1772743255</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1772743255</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/서초_PT.xlsx
+++ b/naver-place-crawler/results_health/서초_PT.xlsx
@@ -421,12 +421,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="43" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>고마워휘트니스 교대PT</t>
+          <t>씨엘필라테스 반포점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>gmw1253@naver.com</t>
+          <t>clpilates9@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1455-1284</t>
+          <t>0507-1382-6396</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>서울특별시 서초구 서초중앙로 166 B1 고마워 휘트니스</t>
+          <t>서울 서초구 서초중앙로 209 9층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gmw1253/223435367519</t>
+          <t>https://blog.naver.com/clpilates9</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -606,10 +606,14 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wfgvhue</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -621,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>342</v>
+        <v>111</v>
       </c>
       <c r="Q2" t="n">
-        <v>1638</v>
+        <v>588</v>
       </c>
       <c r="R2" t="n">
-        <v>1980</v>
+        <v>699</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,12 +640,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>11875969</t>
+          <t>2014815734</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/11875969</t>
+          <t>https://m.place.naver.com/place/2014815734</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -653,34 +657,34 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>씨엘필라테스 반포점</t>
+          <t>고마워휘트니스 교대PT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>clpilates9@naver.com</t>
+          <t>gmw1253@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1382-6396</t>
+          <t>0507-1455-1284</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>서울 서초구 서초중앙로 209 9층</t>
+          <t>서울 서초구 서초중앙로 166 B1 고마워 휘트니스</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/clpilates9</t>
+          <t>https://blog.naver.com/gmw1253/223435367519</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -705,7 +709,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wfgvhue</t>
+          <t>https://talk.naver.com/ct/w42d0n</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -719,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>111</v>
+        <v>342</v>
       </c>
       <c r="Q3" t="n">
-        <v>588</v>
+        <v>1639</v>
       </c>
       <c r="R3" t="n">
-        <v>699</v>
+        <v>1981</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -734,12 +738,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2014815734</t>
+          <t>11875969</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2014815734</t>
+          <t>https://m.place.naver.com/place/11875969</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -773,7 +777,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>서울특별시 서초구 서초대로 320 K타워 B2층 에이블짐 교대역점</t>
+          <t>서울 서초구 서초대로 320 K타워 B2층 에이블짐 교대역점</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -798,10 +802,14 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wc3uli</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -863,7 +871,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>서울특별시 서초구 서초대로78길 38 5층</t>
+          <t>서울 서초구 서초대로78길 38 5층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -888,10 +896,14 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4bf2n</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -903,13 +915,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="Q5" t="n">
         <v>1397</v>
       </c>
       <c r="R5" t="n">
-        <v>1716</v>
+        <v>1715</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -957,7 +969,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>서울특별시 서초구 사임당로 174 강남미래타워 지하1층</t>
+          <t>서울 서초구 사임당로 174 강남미래타워 지하1층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -982,10 +994,14 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4x4b9</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1047,7 +1063,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>서울특별시 서초구 강남대로53길 7 애니타워 301호 강남역 PT 바디스펙트럼</t>
+          <t>서울 서초구 강남대로53길 7 애니타워 301호 강남역 PT 바디스펙트럼</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1072,10 +1088,14 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wc1zvs</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>O</t>
@@ -1090,10 +1110,10 @@
         <v>116</v>
       </c>
       <c r="Q7" t="n">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="R7" t="n">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1141,7 +1161,7 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울특별시 서초구 사평대로56길 7 서초한일유앤아이주상복합 지하2층</t>
+          <t>서울 서초구 사평대로56길 7 서초한일유앤아이주상복합 지하2층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1166,10 +1186,14 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wsa11ia</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1213,34 +1237,34 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>휴메이크휘트니스 강남점</t>
+          <t>듀오핏</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>humake001@naver.com</t>
+          <t>duofit@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1432-0174</t>
+          <t>0507-1485-7224</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울특별시 서초구 강남대로 327 대륭서초타워 지하2층</t>
+          <t>서울 서초구 사평대로2길 22 2층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/humakefitness_gn</t>
+          <t>https://www.instagram.com/duofit_official</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1260,10 +1284,14 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w42jrm</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1275,13 +1303,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1019</v>
+        <v>18</v>
       </c>
       <c r="Q9" t="n">
-        <v>1272</v>
+        <v>57</v>
       </c>
       <c r="R9" t="n">
-        <v>2291</v>
+        <v>75</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1290,12 +1318,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>20077206</t>
+          <t>1242559598</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20077206</t>
+          <t>https://m.place.naver.com/place/1242559598</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1307,34 +1335,34 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>트리니티 PT Pilates LAB</t>
+          <t>휴메이크휘트니스 강남점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>trinity_pt@naver.com</t>
+          <t>humake001@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-2097-3213</t>
+          <t>0507-1432-0174</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울 서초구 서초대로48길 107 6층</t>
+          <t>서울 서초구 강남대로 327 대륭서초타워 지하2층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/trinity_pt</t>
+          <t>http://www.instagram.com/humakefitness_gn</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1349,7 +1377,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1359,7 +1387,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wg58axz</t>
+          <t>https://talk.naver.com/ct/w4s52g</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1373,13 +1401,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>74</v>
+        <v>1019</v>
       </c>
       <c r="Q10" t="n">
-        <v>98</v>
+        <v>1272</v>
       </c>
       <c r="R10" t="n">
-        <v>172</v>
+        <v>2291</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,12 +1416,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1015744638</t>
+          <t>20077206</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1015744638</t>
+          <t>https://m.place.naver.com/place/20077206</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1405,34 +1433,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>크레이지독스짐</t>
+          <t>리프레쉬클럽 PT 반포래미안점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>bodyartist7@naver.com</t>
+          <t>refreshbanpo@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1314-7087</t>
+          <t>0507-1402-8731</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울특별시 서초구 효령로31길 10 지하 1층</t>
+          <t>서울 서초구 반포대로 287 래미안퍼스티지중심상가 3층 327호, 328호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bodyartist7</t>
+          <t>https://blog.naver.com/refreshbanpo</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1452,10 +1480,14 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4mb8k</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1467,13 +1499,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>789</v>
+        <v>302</v>
       </c>
       <c r="Q11" t="n">
-        <v>400</v>
+        <v>353</v>
       </c>
       <c r="R11" t="n">
-        <v>1189</v>
+        <v>655</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1482,12 +1514,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1659233801</t>
+          <t>20451191</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1659233801</t>
+          <t>https://m.place.naver.com/place/20451191</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1504,29 +1536,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>피치짐PT&amp;필라테스 서초점</t>
+          <t>짐에브리원PT 방배이수점</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>peachgym1@naver.com</t>
+          <t>speedangel26@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1363-0878</t>
+          <t>0507-1362-1331</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>서울특별시 서초구 명달로20길 21 1층 피치짐</t>
+          <t>서울 서초구 서초대로 3-4 디오슈페리움1차 413-1호</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/peachgym1</t>
+          <t>https://blog.naver.com/speedangel26/222432679411</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1546,10 +1578,14 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4ps7j</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr">
         <is>
           <t>X</t>
@@ -1557,17 +1593,17 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>396</v>
+        <v>280</v>
       </c>
       <c r="Q12" t="n">
-        <v>379</v>
+        <v>356</v>
       </c>
       <c r="R12" t="n">
-        <v>775</v>
+        <v>636</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1576,12 +1612,12 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1387134259</t>
+          <t>1403416985</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1387134259</t>
+          <t>https://m.place.naver.com/place/1403416985</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1593,30 +1629,34 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>복싱,권투장</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>잽트레이닝 복싱 교대점</t>
+          <t>휴메이크휘트니스 서초점</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>jab_training@naver.com</t>
+          <t>humakesc@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0507-1352-4800</t>
+        </is>
+      </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>서울 서초구 서초중앙로22길 53 지하1층</t>
+          <t>서울 서초구 반포대로 34 로얄빌딩 지하1층 휴메이크휘트니스 서초점</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://cafe.naver.com/jabtraining?iframe_url=/MyCafeIntro.nhn%3Fclubid=31590001</t>
+          <t>https://blog.naver.com/humakesc</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1636,10 +1676,14 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4s52m</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr">
         <is>
           <t>X</t>
@@ -1651,13 +1695,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>140</v>
+        <v>773</v>
       </c>
       <c r="Q13" t="n">
-        <v>4</v>
+        <v>1015</v>
       </c>
       <c r="R13" t="n">
-        <v>144</v>
+        <v>1788</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1666,12 +1710,12 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1772743255</t>
+          <t>32308075</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1772743255</t>
+          <t>https://m.place.naver.com/place/32308075</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">

--- a/naver-place-crawler/results_health/서초_PT.xlsx
+++ b/naver-place-crawler/results_health/서초_PT.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V13"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -426,13 +426,13 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="43" customWidth="1" min="7" max="7"/>
+    <col width="46" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>씨엘필라테스 반포점</t>
+          <t>고마워휘트니스 교대PT</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>clpilates9@naver.com</t>
+          <t>gmw1253@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1382-6396</t>
+          <t>0507-1455-1284</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>서울 서초구 서초중앙로 209 9층</t>
+          <t>서울특별시 서초구 서초중앙로 166 B1 고마워 휘트니스</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/clpilates9</t>
+          <t>https://blog.naver.com/gmw1253/223435367519</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -606,14 +606,10 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wfgvhue</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -625,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>111</v>
+        <v>342</v>
       </c>
       <c r="Q2" t="n">
-        <v>588</v>
+        <v>1637</v>
       </c>
       <c r="R2" t="n">
-        <v>699</v>
+        <v>1979</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,12 +636,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2014815734</t>
+          <t>11875969</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2014815734</t>
+          <t>https://m.place.naver.com/place/11875969</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -657,34 +653,34 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>고마워휘트니스 교대PT</t>
+          <t>에이블짐 교대역점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>gmw1253@naver.com</t>
+          <t>ablegym7@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1455-1284</t>
+          <t>0507-1332-1816</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>서울 서초구 서초중앙로 166 B1 고마워 휘트니스</t>
+          <t>서울특별시 서초구 서초대로 320 K타워 B2층 에이블짐 교대역점</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gmw1253/223435367519</t>
+          <t>https://blog.naver.com/ablegym7</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -704,14 +700,10 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w42d0n</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -723,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>342</v>
+        <v>1972</v>
       </c>
       <c r="Q3" t="n">
-        <v>1639</v>
+        <v>1606</v>
       </c>
       <c r="R3" t="n">
-        <v>1981</v>
+        <v>3578</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,12 +730,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>11875969</t>
+          <t>1486596721</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/11875969</t>
+          <t>https://m.place.naver.com/place/1486596721</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -760,34 +752,34 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>에이블짐 교대역점</t>
+          <t>MN휘트니스 헬스 PT 강남역점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ablegym7@naver.com</t>
+          <t>mnfitness1@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1332-1816</t>
+          <t>0507-1361-0000</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>서울 서초구 서초대로 320 K타워 B2층 에이블짐 교대역점</t>
+          <t>서울특별시 서초구 사임당로 174 강남미래타워 지하1층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ablegym7</t>
+          <t>http://www.mnkorea.kr</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -802,14 +794,10 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wc3uli</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -821,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1972</v>
+        <v>964</v>
       </c>
       <c r="Q4" t="n">
-        <v>1606</v>
+        <v>998</v>
       </c>
       <c r="R4" t="n">
-        <v>3578</v>
+        <v>1962</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,12 +824,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1486596721</t>
+          <t>36615340</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1486596721</t>
+          <t>https://m.place.naver.com/place/36615340</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -871,7 +859,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>서울 서초구 서초대로78길 38 5층</t>
+          <t>서울특별시 서초구 서초대로78길 38 5층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -896,14 +884,10 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4bf2n</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -918,10 +902,10 @@
         <v>318</v>
       </c>
       <c r="Q5" t="n">
-        <v>1397</v>
+        <v>1400</v>
       </c>
       <c r="R5" t="n">
-        <v>1715</v>
+        <v>1718</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -952,29 +936,25 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MN휘트니스 헬스 PT 강남역점</t>
+          <t>강남역 PT 바디스펙트럼</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>mnfitness1@naver.com</t>
+          <t>bodyspectrum@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0507-1361-0000</t>
-        </is>
-      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>서울 서초구 사임당로 174 강남미래타워 지하1층</t>
+          <t>서울특별시 서초구 강남대로53길 7 애니타워 301호 강남역 PT 바디스펙트럼</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>http://www.mnkorea.kr</t>
+          <t>https://bodyspectrum.co.kr/</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -984,7 +964,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -994,17 +974,13 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4x4b9</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1013,13 +989,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>964</v>
+        <v>116</v>
       </c>
       <c r="Q6" t="n">
-        <v>998</v>
+        <v>853</v>
       </c>
       <c r="R6" t="n">
-        <v>1962</v>
+        <v>969</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1028,12 +1004,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>36615340</t>
+          <t>1084545069</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36615340</t>
+          <t>https://m.place.naver.com/place/1084545069</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1050,35 +1026,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>강남역 PT 바디스펙트럼</t>
+          <t>헬스보이짐 필라걸 신논현점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>bodyspectrum@naver.com</t>
+          <t>healthboy45@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0507-1364-7391</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>서울 서초구 강남대로53길 7 애니타워 301호 강남역 PT 바디스펙트럼</t>
+          <t>서울특별시 서초구 사평대로56길 7 서초한일유앤아이주상복합 지하2층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://bodyspectrum.co.kr/</t>
+          <t>https://blog.naver.com/healthboy45</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1088,17 +1068,13 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wc1zvs</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1107,13 +1083,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>116</v>
+        <v>1070</v>
       </c>
       <c r="Q7" t="n">
-        <v>853</v>
+        <v>655</v>
       </c>
       <c r="R7" t="n">
-        <v>969</v>
+        <v>1725</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1122,12 +1098,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1084545069</t>
+          <t>1810083742</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1084545069</t>
+          <t>https://m.place.naver.com/place/1810083742</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1139,34 +1115,34 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>헬스보이짐 필라걸 신논현점</t>
+          <t>휴메이크휘트니스 강남점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>healthboy45@naver.com</t>
+          <t>humake001@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1364-7391</t>
+          <t>0507-1432-0174</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울 서초구 사평대로56길 7 서초한일유앤아이주상복합 지하2층</t>
+          <t>서울특별시 서초구 강남대로 327 대륭서초타워 지하2층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/healthboy45</t>
+          <t>http://www.instagram.com/humakefitness_gn</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1181,19 +1157,15 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wsa11ia</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1205,13 +1177,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1070</v>
+        <v>1019</v>
       </c>
       <c r="Q8" t="n">
-        <v>655</v>
+        <v>1271</v>
       </c>
       <c r="R8" t="n">
-        <v>1725</v>
+        <v>2290</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1220,12 +1192,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1810083742</t>
+          <t>20077206</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1810083742</t>
+          <t>https://m.place.naver.com/place/20077206</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1242,29 +1214,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>듀오핏</t>
+          <t>리프레쉬클럽 PT 반포래미안점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>duofit@naver.com</t>
+          <t>refreshbanpo@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1485-7224</t>
+          <t>0507-1402-8731</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울 서초구 사평대로2길 22 2층</t>
+          <t>서울특별시 서초구 반포대로 287 래미안퍼스티지중심상가 3층 327호, 328호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/duofit_official</t>
+          <t>https://blog.naver.com/refreshbanpo</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1279,19 +1251,15 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w42jrm</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1303,13 +1271,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>18</v>
+        <v>302</v>
       </c>
       <c r="Q9" t="n">
-        <v>57</v>
+        <v>353</v>
       </c>
       <c r="R9" t="n">
-        <v>75</v>
+        <v>655</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1318,12 +1286,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1242559598</t>
+          <t>20451191</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1242559598</t>
+          <t>https://m.place.naver.com/place/20451191</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1335,34 +1303,34 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>휴메이크휘트니스 강남점</t>
+          <t>짐에브리원PT 방배이수점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>humake001@naver.com</t>
+          <t>speedangel26@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1432-0174</t>
+          <t>0507-1362-1331</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울 서초구 강남대로 327 대륭서초타워 지하2층</t>
+          <t>서울특별시 서초구 서초대로 3-4 디오슈페리움1차 413-1호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/humakefitness_gn</t>
+          <t>https://blog.naver.com/speedangel26/222432679411</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1377,19 +1345,15 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4s52g</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1401,13 +1365,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1019</v>
+        <v>280</v>
       </c>
       <c r="Q10" t="n">
-        <v>1272</v>
+        <v>356</v>
       </c>
       <c r="R10" t="n">
-        <v>2291</v>
+        <v>636</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1416,12 +1380,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>20077206</t>
+          <t>1403416985</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20077206</t>
+          <t>https://m.place.naver.com/place/1403416985</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1433,34 +1397,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>리프레쉬클럽 PT 반포래미안점</t>
+          <t>휴메이크휘트니스 서초점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>refreshbanpo@naver.com</t>
+          <t>humakesc@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1402-8731</t>
+          <t>0507-1352-4800</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울 서초구 반포대로 287 래미안퍼스티지중심상가 3층 327호, 328호</t>
+          <t>서울특별시 서초구 반포대로 34 로얄빌딩 지하1층 휴메이크휘트니스 서초점</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/refreshbanpo</t>
+          <t>https://blog.naver.com/humakesc</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1480,14 +1444,10 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4mb8k</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1499,13 +1459,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>302</v>
+        <v>774</v>
       </c>
       <c r="Q11" t="n">
-        <v>353</v>
+        <v>1016</v>
       </c>
       <c r="R11" t="n">
-        <v>655</v>
+        <v>1790</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1514,211 +1474,15 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>20451191</t>
+          <t>32308075</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20451191</t>
+          <t>https://m.place.naver.com/place/32308075</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>짐에브리원PT 방배이수점</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>speedangel26@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0507-1362-1331</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>서울 서초구 서초대로 3-4 디오슈페리움1차 413-1호</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/speedangel26/222432679411</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4ps7j</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>280</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>356</v>
-      </c>
-      <c r="R12" t="n">
-        <v>636</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>1403416985</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1403416985</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>헬스장</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>휴메이크휘트니스 서초점</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>humakesc@naver.com</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0507-1352-4800</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>서울 서초구 반포대로 34 로얄빌딩 지하1층 휴메이크휘트니스 서초점</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/humakesc</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4s52m</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
-        <v>773</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1015</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1788</v>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>32308075</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/32308075</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
         <is>
           <t>2026-04-26</t>
         </is>

--- a/naver-place-crawler/results_health/서초_PT.xlsx
+++ b/naver-place-crawler/results_health/서초_PT.xlsx
@@ -421,18 +421,18 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="46" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -1303,34 +1303,34 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>짐에브리원PT 방배이수점</t>
+          <t>휴메이크휘트니스 서초점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>speedangel26@naver.com</t>
+          <t>humakesc@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1362-1331</t>
+          <t>0507-1352-4800</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울특별시 서초구 서초대로 3-4 디오슈페리움1차 413-1호</t>
+          <t>서울특별시 서초구 반포대로 34 로얄빌딩 지하1층 휴메이크휘트니스 서초점</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/speedangel26/222432679411</t>
+          <t>https://blog.naver.com/humakesc</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1365,13 +1365,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>280</v>
+        <v>774</v>
       </c>
       <c r="Q10" t="n">
-        <v>356</v>
+        <v>1016</v>
       </c>
       <c r="R10" t="n">
-        <v>636</v>
+        <v>1790</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1380,12 +1380,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1403416985</t>
+          <t>32308075</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1403416985</t>
+          <t>https://m.place.naver.com/place/32308075</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1397,34 +1397,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>휴메이크휘트니스 서초점</t>
+          <t>트리니티 PT Pilates LAB</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>humakesc@naver.com</t>
+          <t>trinity_pt@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1352-4800</t>
+          <t>0507-2097-3213</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울특별시 서초구 반포대로 34 로얄빌딩 지하1층 휴메이크휘트니스 서초점</t>
+          <t>서울 서초구 서초대로48길 107 6층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/humakesc</t>
+          <t>https://blog.naver.com/trinity_pt</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1444,10 +1444,14 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wg58axz</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1459,13 +1463,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>774</v>
+        <v>74</v>
       </c>
       <c r="Q11" t="n">
-        <v>1016</v>
+        <v>98</v>
       </c>
       <c r="R11" t="n">
-        <v>1790</v>
+        <v>172</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1474,12 +1478,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>32308075</t>
+          <t>1015744638</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/32308075</t>
+          <t>https://m.place.naver.com/place/1015744638</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">

--- a/naver-place-crawler/results_health/서초_PT.xlsx
+++ b/naver-place-crawler/results_health/서초_PT.xlsx
@@ -427,7 +427,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="46" customWidth="1" min="7" max="7"/>
-    <col width="45" customWidth="1" min="8" max="8"/>
+    <col width="43" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>고마워휘트니스 교대PT</t>
+          <t>헤이븐PT 교대점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>gmw1253@naver.com</t>
+          <t>studio_haven@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1455-1284</t>
+          <t>0507-1410-1595</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>서울특별시 서초구 서초중앙로 166 B1 고마워 휘트니스</t>
+          <t>서울특별시 서초구 서초중앙로28길 6 가정빌딩 4층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gmw1253/223435367519</t>
+          <t>https://blog.naver.com/studio_haven</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -617,17 +617,17 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>342</v>
+        <v>22</v>
       </c>
       <c r="Q2" t="n">
-        <v>1637</v>
+        <v>82</v>
       </c>
       <c r="R2" t="n">
-        <v>1979</v>
+        <v>104</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,51 +636,51 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>11875969</t>
+          <t>37157624</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/11875969</t>
+          <t>https://m.place.naver.com/place/37157624</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>에이블짐 교대역점</t>
+          <t>씨엘필라테스 반포점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ablegym7@naver.com</t>
+          <t>clpilates9@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1332-1816</t>
+          <t>0507-1382-6396</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>서울특별시 서초구 서초대로 320 K타워 B2층 에이블짐 교대역점</t>
+          <t>서울 서초구 서초중앙로 209 9층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ablegym7</t>
+          <t>https://blog.naver.com/clpilates9</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -700,10 +700,14 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wfgvhue</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -715,13 +719,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1972</v>
+        <v>111</v>
       </c>
       <c r="Q3" t="n">
-        <v>1606</v>
+        <v>592</v>
       </c>
       <c r="R3" t="n">
-        <v>3578</v>
+        <v>703</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,17 +734,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1486596721</t>
+          <t>2014815734</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1486596721</t>
+          <t>https://m.place.naver.com/place/2014815734</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -752,34 +756,34 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MN휘트니스 헬스 PT 강남역점</t>
+          <t>에이블짐 교대역점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>mnfitness1@naver.com</t>
+          <t>ablegym7@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1361-0000</t>
+          <t>0507-1332-1816</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>서울특별시 서초구 사임당로 174 강남미래타워 지하1층</t>
+          <t>서울특별시 서초구 서초대로 320 K타워 B2층 에이블짐 교대역점</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>http://www.mnkorea.kr</t>
+          <t>https://blog.naver.com/ablegym7</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -809,13 +813,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>964</v>
+        <v>1972</v>
       </c>
       <c r="Q4" t="n">
-        <v>998</v>
+        <v>1606</v>
       </c>
       <c r="R4" t="n">
-        <v>1962</v>
+        <v>3578</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,17 +828,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>36615340</t>
+          <t>1486596721</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36615340</t>
+          <t>https://m.place.naver.com/place/1486596721</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -846,30 +850,34 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>아고라피트니스 헬스&amp;PT 강남역점</t>
+          <t>MN휘트니스 헬스 PT 강남역점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>agorablog@naver.com</t>
+          <t>mnfitness1@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0507-1361-0000</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>서울특별시 서초구 서초대로78길 38 5층</t>
+          <t>서울특별시 서초구 사임당로 174 강남미래타워 지하1층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/agorablog</t>
+          <t>http://www.mnkorea.kr</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -899,13 +907,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>318</v>
+        <v>963</v>
       </c>
       <c r="Q5" t="n">
-        <v>1400</v>
+        <v>998</v>
       </c>
       <c r="R5" t="n">
-        <v>1718</v>
+        <v>1961</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -914,17 +922,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1034599129</t>
+          <t>36615340</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1034599129</t>
+          <t>https://m.place.naver.com/place/36615340</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -936,12 +944,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>강남역 PT 바디스펙트럼</t>
+          <t>아고라피트니스 헬스&amp;PT 강남역점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>bodyspectrum@naver.com</t>
+          <t>agorablog@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -949,22 +957,22 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>서울특별시 서초구 강남대로53길 7 애니타워 301호 강남역 PT 바디스펙트럼</t>
+          <t>서울특별시 서초구 서초대로78길 38 5층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://bodyspectrum.co.kr/</t>
+          <t>https://blog.naver.com/agorablog</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -980,7 +988,7 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -989,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>116</v>
+        <v>318</v>
       </c>
       <c r="Q6" t="n">
-        <v>853</v>
+        <v>1400</v>
       </c>
       <c r="R6" t="n">
-        <v>969</v>
+        <v>1718</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1004,17 +1012,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1084545069</t>
+          <t>1034599129</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1084545069</t>
+          <t>https://m.place.naver.com/place/1034599129</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1026,29 +1034,25 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>헬스보이짐 필라걸 신논현점</t>
+          <t>강남역 PT 바디스펙트럼</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>healthboy45@naver.com</t>
+          <t>bodyspectrum@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0507-1364-7391</t>
-        </is>
-      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>서울특별시 서초구 사평대로56길 7 서초한일유앤아이주상복합 지하2층</t>
+          <t>서울특별시 서초구 강남대로53길 7 애니타워 301호 강남역 PT 바디스펙트럼</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/healthboy45</t>
+          <t>https://bodyspectrum.co.kr/</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1063,7 +1067,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1083,13 +1087,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1070</v>
+        <v>116</v>
       </c>
       <c r="Q7" t="n">
-        <v>655</v>
+        <v>854</v>
       </c>
       <c r="R7" t="n">
-        <v>1725</v>
+        <v>970</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1098,51 +1102,51 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1810083742</t>
+          <t>1084545069</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1810083742</t>
+          <t>https://m.place.naver.com/place/1084545069</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>휴메이크휘트니스 강남점</t>
+          <t>헬스보이짐 필라걸 신논현점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>humake001@naver.com</t>
+          <t>healthboy45@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1432-0174</t>
+          <t>0507-1364-7391</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울특별시 서초구 강남대로 327 대륭서초타워 지하2층</t>
+          <t>서울특별시 서초구 사평대로56길 7 서초한일유앤아이주상복합 지하2층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/humakefitness_gn</t>
+          <t>https://blog.naver.com/healthboy45</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1157,7 +1161,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1177,13 +1181,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1019</v>
+        <v>1070</v>
       </c>
       <c r="Q8" t="n">
-        <v>1271</v>
+        <v>655</v>
       </c>
       <c r="R8" t="n">
-        <v>2290</v>
+        <v>1725</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1192,17 +1196,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>20077206</t>
+          <t>1810083742</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20077206</t>
+          <t>https://m.place.naver.com/place/1810083742</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1296,7 +1300,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1308,29 +1312,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>휴메이크휘트니스 서초점</t>
+          <t>휴메이크휘트니스 강남점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>humakesc@naver.com</t>
+          <t>humake001@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1352-4800</t>
+          <t>0507-1432-0174</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울특별시 서초구 반포대로 34 로얄빌딩 지하1층 휴메이크휘트니스 서초점</t>
+          <t>서울특별시 서초구 강남대로 327 대륭서초타워 지하2층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/humakesc</t>
+          <t>http://www.instagram.com/humakefitness_gn</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1345,7 +1349,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1365,13 +1369,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>774</v>
+        <v>1019</v>
       </c>
       <c r="Q10" t="n">
-        <v>1016</v>
+        <v>1271</v>
       </c>
       <c r="R10" t="n">
-        <v>1790</v>
+        <v>2290</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1380,17 +1384,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>32308075</t>
+          <t>20077206</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/32308075</t>
+          <t>https://m.place.naver.com/place/20077206</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1488,7 +1492,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/서초_PT.xlsx
+++ b/naver-place-crawler/results_health/서초_PT.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -427,7 +427,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="46" customWidth="1" min="7" max="7"/>
-    <col width="43" customWidth="1" min="8" max="8"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -653,34 +653,34 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>씨엘필라테스 반포점</t>
+          <t>고마워휘트니스 교대PT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>clpilates9@naver.com</t>
+          <t>gmw1253@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1382-6396</t>
+          <t>0507-1455-1284</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>서울 서초구 서초중앙로 209 9층</t>
+          <t>서울특별시 서초구 서초중앙로 166 B1 고마워 휘트니스</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/clpilates9</t>
+          <t>https://blog.naver.com/gmw1253/223435367519</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -700,14 +700,10 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wfgvhue</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -719,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>111</v>
+        <v>342</v>
       </c>
       <c r="Q3" t="n">
-        <v>592</v>
+        <v>1639</v>
       </c>
       <c r="R3" t="n">
-        <v>703</v>
+        <v>1981</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -734,12 +730,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2014815734</t>
+          <t>11875969</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2014815734</t>
+          <t>https://m.place.naver.com/place/11875969</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -1000,10 +996,10 @@
         <v>318</v>
       </c>
       <c r="Q6" t="n">
-        <v>1400</v>
+        <v>1403</v>
       </c>
       <c r="R6" t="n">
-        <v>1718</v>
+        <v>1721</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1057,17 +1053,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1078,7 +1074,7 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1090,10 +1086,10 @@
         <v>116</v>
       </c>
       <c r="Q7" t="n">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="R7" t="n">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1401,96 +1397,190 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>트리니티 PT Pilates LAB</t>
+          <t>휴메이크휘트니스 서초점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>trinity_pt@naver.com</t>
+          <t>humakesc@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-2097-3213</t>
+          <t>0507-1352-4800</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
+          <t>서울특별시 서초구 반포대로 34 로얄빌딩 지하1층 휴메이크휘트니스 서초점</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/humakesc</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>774</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1017</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1791</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>32308075</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/32308075</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>트리니티 PT Pilates LAB</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>trinity_pt@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-2097-3213</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
           <t>서울 서초구 서초대로48길 107 6층</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>https://blog.naver.com/trinity_pt</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
         <is>
           <t>https://talk.naver.com/ct/wg58axz</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P11" t="n">
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
         <v>74</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="Q12" t="n">
         <v>98</v>
       </c>
-      <c r="R11" t="n">
+      <c r="R12" t="n">
         <v>172</v>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
         <is>
           <t>1015744638</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/1015744638</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>

--- a/naver-place-crawler/results_health/서초_PT.xlsx
+++ b/naver-place-crawler/results_health/서초_PT.xlsx
@@ -421,7 +421,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
@@ -653,34 +653,34 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>고마워휘트니스 교대PT</t>
+          <t>씨엘필라테스 반포점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>gmw1253@naver.com</t>
+          <t>clpilates9@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1455-1284</t>
+          <t>0507-1382-6396</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>서울특별시 서초구 서초중앙로 166 B1 고마워 휘트니스</t>
+          <t>서울 서초구 서초중앙로 209 9층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gmw1253/223435367519</t>
+          <t>https://blog.naver.com/clpilates9</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -700,10 +700,14 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wfgvhue</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -715,13 +719,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>342</v>
+        <v>112</v>
       </c>
       <c r="Q3" t="n">
-        <v>1639</v>
+        <v>597</v>
       </c>
       <c r="R3" t="n">
-        <v>1981</v>
+        <v>709</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,12 +734,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>11875969</t>
+          <t>2014815734</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/11875969</t>
+          <t>https://m.place.naver.com/place/2014815734</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -747,34 +751,34 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>에이블짐 교대역점</t>
+          <t>고마워휘트니스 교대PT</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ablegym7@naver.com</t>
+          <t>gmw1253@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1332-1816</t>
+          <t>0507-1455-1284</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>서울특별시 서초구 서초대로 320 K타워 B2층 에이블짐 교대역점</t>
+          <t>서울특별시 서초구 서초중앙로 166 B1 고마워 휘트니스</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ablegym7</t>
+          <t>https://blog.naver.com/gmw1253/223435367519</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -809,13 +813,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1972</v>
+        <v>342</v>
       </c>
       <c r="Q4" t="n">
-        <v>1606</v>
+        <v>1639</v>
       </c>
       <c r="R4" t="n">
-        <v>3578</v>
+        <v>1981</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,12 +828,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1486596721</t>
+          <t>11875969</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1486596721</t>
+          <t>https://m.place.naver.com/place/11875969</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -846,34 +850,34 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MN휘트니스 헬스 PT 강남역점</t>
+          <t>에이블짐 교대역점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>mnfitness1@naver.com</t>
+          <t>ablegym7@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1361-0000</t>
+          <t>0507-1332-1816</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>서울특별시 서초구 사임당로 174 강남미래타워 지하1층</t>
+          <t>서울특별시 서초구 서초대로 320 K타워 B2층 에이블짐 교대역점</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>http://www.mnkorea.kr</t>
+          <t>https://blog.naver.com/ablegym7</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -903,13 +907,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>963</v>
+        <v>1973</v>
       </c>
       <c r="Q5" t="n">
-        <v>998</v>
+        <v>1606</v>
       </c>
       <c r="R5" t="n">
-        <v>1961</v>
+        <v>3579</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,12 +922,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>36615340</t>
+          <t>1486596721</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36615340</t>
+          <t>https://m.place.naver.com/place/1486596721</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -940,30 +944,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>아고라피트니스 헬스&amp;PT 강남역점</t>
+          <t>MN휘트니스 헬스 PT 강남역점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>agorablog@naver.com</t>
+          <t>mnfitness1@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0507-1361-0000</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>서울특별시 서초구 서초대로78길 38 5층</t>
+          <t>서울특별시 서초구 사임당로 174 강남미래타워 지하1층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/agorablog</t>
+          <t>http://www.mnkorea.kr</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -993,13 +1001,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>318</v>
+        <v>963</v>
       </c>
       <c r="Q6" t="n">
-        <v>1403</v>
+        <v>998</v>
       </c>
       <c r="R6" t="n">
-        <v>1721</v>
+        <v>1961</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1008,12 +1016,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1034599129</t>
+          <t>36615340</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1034599129</t>
+          <t>https://m.place.naver.com/place/36615340</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1030,12 +1038,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>강남역 PT 바디스펙트럼</t>
+          <t>아고라피트니스 헬스&amp;PT 강남역점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>bodyspectrum@naver.com</t>
+          <t>agorablog@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -1043,22 +1051,22 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>서울특별시 서초구 강남대로53길 7 애니타워 301호 강남역 PT 바디스펙트럼</t>
+          <t>서울특별시 서초구 서초대로78길 38 5층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://bodyspectrum.co.kr/</t>
+          <t>https://blog.naver.com/agorablog</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1074,7 +1082,7 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1083,13 +1091,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>116</v>
+        <v>318</v>
       </c>
       <c r="Q7" t="n">
-        <v>855</v>
+        <v>1403</v>
       </c>
       <c r="R7" t="n">
-        <v>971</v>
+        <v>1721</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1098,12 +1106,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1084545069</t>
+          <t>1034599129</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1084545069</t>
+          <t>https://m.place.naver.com/place/1034599129</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1120,39 +1128,35 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>헬스보이짐 필라걸 신논현점</t>
+          <t>강남역 PT 바디스펙트럼</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>healthboy45@naver.com</t>
+          <t>bodyspectrum@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0507-1364-7391</t>
-        </is>
-      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울특별시 서초구 사평대로56길 7 서초한일유앤아이주상복합 지하2층</t>
+          <t>서울특별시 서초구 강남대로53길 7 애니타워 301호 강남역 PT 바디스펙트럼</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/healthboy45</t>
+          <t>https://bodyspectrum.co.kr/</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1168,7 +1172,7 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1177,13 +1181,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1070</v>
+        <v>116</v>
       </c>
       <c r="Q8" t="n">
-        <v>655</v>
+        <v>855</v>
       </c>
       <c r="R8" t="n">
-        <v>1725</v>
+        <v>971</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1192,12 +1196,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1810083742</t>
+          <t>1084545069</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1810083742</t>
+          <t>https://m.place.naver.com/place/1084545069</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1214,29 +1218,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>리프레쉬클럽 PT 반포래미안점</t>
+          <t>헬스보이짐 필라걸 신논현점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>refreshbanpo@naver.com</t>
+          <t>healthboy45@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1402-8731</t>
+          <t>0507-1364-7391</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울특별시 서초구 반포대로 287 래미안퍼스티지중심상가 3층 327호, 328호</t>
+          <t>서울특별시 서초구 사평대로56길 7 서초한일유앤아이주상복합 지하2층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/refreshbanpo</t>
+          <t>https://blog.naver.com/healthboy45</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1271,13 +1275,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>302</v>
+        <v>1071</v>
       </c>
       <c r="Q9" t="n">
-        <v>353</v>
+        <v>656</v>
       </c>
       <c r="R9" t="n">
-        <v>655</v>
+        <v>1727</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1286,12 +1290,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>20451191</t>
+          <t>1810083742</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20451191</t>
+          <t>https://m.place.naver.com/place/1810083742</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1303,34 +1307,34 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>휴메이크휘트니스 강남점</t>
+          <t>리프레쉬클럽 PT 반포래미안점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>humake001@naver.com</t>
+          <t>refreshbanpo@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1432-0174</t>
+          <t>0507-1402-8731</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울특별시 서초구 강남대로 327 대륭서초타워 지하2층</t>
+          <t>서울특별시 서초구 반포대로 287 래미안퍼스티지중심상가 3층 327호, 328호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/humakefitness_gn</t>
+          <t>https://blog.naver.com/refreshbanpo</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1345,7 +1349,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1365,13 +1369,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1019</v>
+        <v>302</v>
       </c>
       <c r="Q10" t="n">
-        <v>1271</v>
+        <v>353</v>
       </c>
       <c r="R10" t="n">
-        <v>2290</v>
+        <v>655</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1380,12 +1384,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>20077206</t>
+          <t>20451191</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20077206</t>
+          <t>https://m.place.naver.com/place/20451191</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1402,29 +1406,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>휴메이크휘트니스 서초점</t>
+          <t>휴메이크휘트니스 강남점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>humakesc@naver.com</t>
+          <t>humake001@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1352-4800</t>
+          <t>0507-1432-0174</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울특별시 서초구 반포대로 34 로얄빌딩 지하1층 휴메이크휘트니스 서초점</t>
+          <t>서울특별시 서초구 강남대로 327 대륭서초타워 지하2층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/humakesc</t>
+          <t>http://www.instagram.com/humakefitness_gn</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1439,7 +1443,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1459,13 +1463,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>774</v>
+        <v>1019</v>
       </c>
       <c r="Q11" t="n">
-        <v>1017</v>
+        <v>1271</v>
       </c>
       <c r="R11" t="n">
-        <v>1791</v>
+        <v>2290</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1474,12 +1478,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>32308075</t>
+          <t>20077206</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/32308075</t>
+          <t>https://m.place.naver.com/place/20077206</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1491,34 +1495,34 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>트리니티 PT Pilates LAB</t>
+          <t>휴메이크휘트니스 서초점</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>trinity_pt@naver.com</t>
+          <t>humakesc@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-2097-3213</t>
+          <t>0507-1352-4800</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>서울 서초구 서초대로48길 107 6층</t>
+          <t>서울특별시 서초구 반포대로 34 로얄빌딩 지하1층 휴메이크휘트니스 서초점</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/trinity_pt</t>
+          <t>https://blog.naver.com/humakesc</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1538,14 +1542,10 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wg58axz</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
           <t>X</t>
@@ -1557,13 +1557,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>74</v>
+        <v>774</v>
       </c>
       <c r="Q12" t="n">
-        <v>98</v>
+        <v>1020</v>
       </c>
       <c r="R12" t="n">
-        <v>172</v>
+        <v>1794</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1572,12 +1572,12 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1015744638</t>
+          <t>32308075</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1015744638</t>
+          <t>https://m.place.naver.com/place/32308075</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">

--- a/naver-place-crawler/results_health/서초_PT.xlsx
+++ b/naver-place-crawler/results_health/서초_PT.xlsx
@@ -421,7 +421,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
@@ -432,7 +432,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -646,41 +646,41 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>씨엘필라테스 반포점</t>
+          <t>고마워휘트니스 교대PT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>clpilates9@naver.com</t>
+          <t>gmw1253@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1382-6396</t>
+          <t>0507-1455-1284</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>서울 서초구 서초중앙로 209 9층</t>
+          <t>서울특별시 서초구 서초중앙로 166 B1 고마워 휘트니스</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/clpilates9</t>
+          <t>https://blog.naver.com/gmw1253/223435367519</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -700,14 +700,10 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wfgvhue</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -719,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>112</v>
+        <v>342</v>
       </c>
       <c r="Q3" t="n">
-        <v>597</v>
+        <v>1640</v>
       </c>
       <c r="R3" t="n">
-        <v>709</v>
+        <v>1982</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -734,51 +730,51 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2014815734</t>
+          <t>11875969</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2014815734</t>
+          <t>https://m.place.naver.com/place/11875969</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>고마워휘트니스 교대PT</t>
+          <t>에이블짐 교대역점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>gmw1253@naver.com</t>
+          <t>ablegym7@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1455-1284</t>
+          <t>0507-1332-1816</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>서울특별시 서초구 서초중앙로 166 B1 고마워 휘트니스</t>
+          <t>서울특별시 서초구 서초대로 320 K타워 B2층 에이블짐 교대역점</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gmw1253/223435367519</t>
+          <t>https://blog.naver.com/ablegym7</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -813,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>342</v>
+        <v>1974</v>
       </c>
       <c r="Q4" t="n">
-        <v>1639</v>
+        <v>1606</v>
       </c>
       <c r="R4" t="n">
-        <v>1981</v>
+        <v>3580</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -828,17 +824,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>11875969</t>
+          <t>1486596721</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/11875969</t>
+          <t>https://m.place.naver.com/place/1486596721</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -850,34 +846,34 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>에이블짐 교대역점</t>
+          <t>MN휘트니스 헬스 PT 강남역점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ablegym7@naver.com</t>
+          <t>mnfitness1@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1332-1816</t>
+          <t>0507-1361-0000</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>서울특별시 서초구 서초대로 320 K타워 B2층 에이블짐 교대역점</t>
+          <t>서울특별시 서초구 사임당로 174 강남미래타워 지하1층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ablegym7</t>
+          <t>http://www.mnkorea.kr</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -907,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1973</v>
+        <v>963</v>
       </c>
       <c r="Q5" t="n">
-        <v>1606</v>
+        <v>998</v>
       </c>
       <c r="R5" t="n">
-        <v>3579</v>
+        <v>1961</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -922,17 +918,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1486596721</t>
+          <t>36615340</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1486596721</t>
+          <t>https://m.place.naver.com/place/36615340</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -944,34 +940,30 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MN휘트니스 헬스 PT 강남역점</t>
+          <t>아고라피트니스 헬스&amp;PT 강남역점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>mnfitness1@naver.com</t>
+          <t>agorablog@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0507-1361-0000</t>
-        </is>
-      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>서울특별시 서초구 사임당로 174 강남미래타워 지하1층</t>
+          <t>서울특별시 서초구 서초대로78길 38 5층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>http://www.mnkorea.kr</t>
+          <t>https://blog.naver.com/agorablog</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1001,13 +993,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>963</v>
+        <v>318</v>
       </c>
       <c r="Q6" t="n">
-        <v>998</v>
+        <v>1403</v>
       </c>
       <c r="R6" t="n">
-        <v>1961</v>
+        <v>1721</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1016,17 +1008,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>36615340</t>
+          <t>1034599129</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36615340</t>
+          <t>https://m.place.naver.com/place/1034599129</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1038,12 +1030,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>아고라피트니스 헬스&amp;PT 강남역점</t>
+          <t>강남역 PT 바디스펙트럼</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>agorablog@naver.com</t>
+          <t>bodyspectrum@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -1051,22 +1043,22 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>서울특별시 서초구 서초대로78길 38 5층</t>
+          <t>서울특별시 서초구 강남대로53길 7 애니타워 301호 강남역 PT 바디스펙트럼</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/agorablog</t>
+          <t>https://bodyspectrum.co.kr/</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1082,7 +1074,7 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1091,13 +1083,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>318</v>
+        <v>116</v>
       </c>
       <c r="Q7" t="n">
-        <v>1403</v>
+        <v>856</v>
       </c>
       <c r="R7" t="n">
-        <v>1721</v>
+        <v>972</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,17 +1098,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1034599129</t>
+          <t>1084545069</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1034599129</t>
+          <t>https://m.place.naver.com/place/1084545069</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1128,35 +1120,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>강남역 PT 바디스펙트럼</t>
+          <t>헬스보이짐 필라걸 신논현점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>bodyspectrum@naver.com</t>
+          <t>healthboy45@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0507-1364-7391</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울특별시 서초구 강남대로53길 7 애니타워 301호 강남역 PT 바디스펙트럼</t>
+          <t>서울특별시 서초구 사평대로56길 7 서초한일유앤아이주상복합 지하2층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://bodyspectrum.co.kr/</t>
+          <t>https://blog.naver.com/healthboy45</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1172,7 +1168,7 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1181,13 +1177,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>116</v>
+        <v>1072</v>
       </c>
       <c r="Q8" t="n">
-        <v>855</v>
+        <v>656</v>
       </c>
       <c r="R8" t="n">
-        <v>971</v>
+        <v>1728</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1196,51 +1192,51 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1084545069</t>
+          <t>1810083742</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1084545069</t>
+          <t>https://m.place.naver.com/place/1810083742</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>헬스보이짐 필라걸 신논현점</t>
+          <t>휴메이크휘트니스 강남점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>healthboy45@naver.com</t>
+          <t>humake001@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1364-7391</t>
+          <t>0507-1432-0174</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울특별시 서초구 사평대로56길 7 서초한일유앤아이주상복합 지하2층</t>
+          <t>서울특별시 서초구 강남대로 327 대륭서초타워 지하2층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/healthboy45</t>
+          <t>http://www.instagram.com/humakefitness_gn</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1255,7 +1251,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1275,13 +1271,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1071</v>
+        <v>1019</v>
       </c>
       <c r="Q9" t="n">
-        <v>656</v>
+        <v>1271</v>
       </c>
       <c r="R9" t="n">
-        <v>1727</v>
+        <v>2290</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1290,17 +1286,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1810083742</t>
+          <t>20077206</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1810083742</t>
+          <t>https://m.place.naver.com/place/20077206</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1394,41 +1390,41 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>휴메이크휘트니스 강남점</t>
+          <t>트리니티 PT Pilates LAB</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>humake001@naver.com</t>
+          <t>trinity_pt@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1432-0174</t>
+          <t>0507-2097-3213</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울특별시 서초구 강남대로 327 대륭서초타워 지하2층</t>
+          <t>서울특별시 서초구 서초대로48길 107 6층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/humakefitness_gn</t>
+          <t>https://blog.naver.com/trinity_pt</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1443,7 +1439,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1463,13 +1459,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1019</v>
+        <v>74</v>
       </c>
       <c r="Q11" t="n">
-        <v>1271</v>
+        <v>99</v>
       </c>
       <c r="R11" t="n">
-        <v>2290</v>
+        <v>173</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1478,51 +1474,51 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>20077206</t>
+          <t>1015744638</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20077206</t>
+          <t>https://m.place.naver.com/place/1015744638</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>휴메이크휘트니스 서초점</t>
+          <t>바디어필 PT 방배점</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>humakesc@naver.com</t>
+          <t>g_y44@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1352-4800</t>
+          <t>0507-1379-9204</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>서울특별시 서초구 반포대로 34 로얄빌딩 지하1층 휴메이크휘트니스 서초점</t>
+          <t>서울특별시 서초구 방배로6길 13 배영빌딩 지하1층</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/humakesc</t>
+          <t>https://blog.naver.com/g_y44</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1557,13 +1553,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>774</v>
+        <v>208</v>
       </c>
       <c r="Q12" t="n">
-        <v>1020</v>
+        <v>168</v>
       </c>
       <c r="R12" t="n">
-        <v>1794</v>
+        <v>376</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1572,17 +1568,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>32308075</t>
+          <t>1027859889</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/32308075</t>
+          <t>https://m.place.naver.com/place/1027859889</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/서초_PT.xlsx
+++ b/naver-place-crawler/results_health/서초_PT.xlsx
@@ -417,11 +417,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
@@ -432,7 +432,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>헤이븐PT 교대점</t>
+          <t>고마워휘트니스 교대PT</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>studio_haven@naver.com</t>
+          <t>gmw1253@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1410-1595</t>
+          <t>0507-1455-1284</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>서울특별시 서초구 서초중앙로28길 6 가정빌딩 4층</t>
+          <t>서울특별시 서초구 서초중앙로 166 B1 고마워 휘트니스</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/studio_haven</t>
+          <t>https://blog.naver.com/gmw1253/223435367519</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -617,17 +617,17 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>22</v>
+        <v>342</v>
       </c>
       <c r="Q2" t="n">
-        <v>82</v>
+        <v>1641</v>
       </c>
       <c r="R2" t="n">
-        <v>104</v>
+        <v>1983</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,12 +636,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>37157624</t>
+          <t>11875969</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37157624</t>
+          <t>https://m.place.naver.com/place/11875969</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -653,34 +653,34 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>고마워휘트니스 교대PT</t>
+          <t>씨엘필라테스 반포점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>gmw1253@naver.com</t>
+          <t>clpilates9@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1455-1284</t>
+          <t>0507-1382-6396</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>서울특별시 서초구 서초중앙로 166 B1 고마워 휘트니스</t>
+          <t>서울 서초구 서초중앙로 209 9층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gmw1253/223435367519</t>
+          <t>https://blog.naver.com/clpilates9</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -700,10 +700,14 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wfgvhue</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -715,13 +719,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>342</v>
+        <v>115</v>
       </c>
       <c r="Q3" t="n">
-        <v>1640</v>
+        <v>601</v>
       </c>
       <c r="R3" t="n">
-        <v>1982</v>
+        <v>716</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,12 +734,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>11875969</t>
+          <t>2014815734</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/11875969</t>
+          <t>https://m.place.naver.com/place/2014815734</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -903,13 +907,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="Q5" t="n">
         <v>998</v>
       </c>
       <c r="R5" t="n">
-        <v>1961</v>
+        <v>1962</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -996,10 +1000,10 @@
         <v>318</v>
       </c>
       <c r="Q6" t="n">
-        <v>1403</v>
+        <v>1396</v>
       </c>
       <c r="R6" t="n">
-        <v>1721</v>
+        <v>1714</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1030,35 +1034,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>강남역 PT 바디스펙트럼</t>
+          <t>헬스보이짐 필라걸 신논현점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>bodyspectrum@naver.com</t>
+          <t>healthboy45@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0507-1364-7391</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>서울특별시 서초구 강남대로53길 7 애니타워 301호 강남역 PT 바디스펙트럼</t>
+          <t>서울특별시 서초구 사평대로56길 7 서초한일유앤아이주상복합 지하2층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://bodyspectrum.co.kr/</t>
+          <t>https://blog.naver.com/healthboy45</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1074,7 +1082,7 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1083,13 +1091,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>116</v>
+        <v>1072</v>
       </c>
       <c r="Q7" t="n">
-        <v>856</v>
+        <v>656</v>
       </c>
       <c r="R7" t="n">
-        <v>972</v>
+        <v>1728</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1098,12 +1106,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1084545069</t>
+          <t>1810083742</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1084545069</t>
+          <t>https://m.place.naver.com/place/1810083742</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1120,29 +1128,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>헬스보이짐 필라걸 신논현점</t>
+          <t>헬링짐 신논현점 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>healthboy45@naver.com</t>
+          <t>healing0201@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1364-7391</t>
+          <t>0507-1460-3368</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울특별시 서초구 사평대로56길 7 서초한일유앤아이주상복합 지하2층</t>
+          <t>서울특별시 서초구 강남대로79길 59 지하 2층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/healthboy45</t>
+          <t>https://blog.naver.com/healing0201</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1177,13 +1185,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1072</v>
+        <v>885</v>
       </c>
       <c r="Q8" t="n">
-        <v>656</v>
+        <v>293</v>
       </c>
       <c r="R8" t="n">
-        <v>1728</v>
+        <v>1178</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1192,12 +1200,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1810083742</t>
+          <t>1611830378</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1810083742</t>
+          <t>https://m.place.naver.com/place/1611830378</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1397,34 +1405,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>트리니티 PT Pilates LAB</t>
+          <t>휴메이크휘트니스 서초점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>trinity_pt@naver.com</t>
+          <t>humakesc@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-2097-3213</t>
+          <t>0507-1352-4800</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울특별시 서초구 서초대로48길 107 6층</t>
+          <t>서울특별시 서초구 반포대로 34 로얄빌딩 지하1층 휴메이크휘트니스 서초점</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/trinity_pt</t>
+          <t>https://blog.naver.com/humakesc</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1459,13 +1467,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>74</v>
+        <v>775</v>
       </c>
       <c r="Q11" t="n">
-        <v>99</v>
+        <v>1024</v>
       </c>
       <c r="R11" t="n">
-        <v>173</v>
+        <v>1799</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1474,109 +1482,15 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1015744638</t>
+          <t>32308075</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1015744638</t>
+          <t>https://m.place.naver.com/place/32308075</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>바디어필 PT 방배점</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>g_y44@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0507-1379-9204</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>서울특별시 서초구 방배로6길 13 배영빌딩 지하1층</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/g_y44</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>208</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>168</v>
-      </c>
-      <c r="R12" t="n">
-        <v>376</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>1027859889</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1027859889</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
         <is>
           <t>2026-04-28</t>
         </is>

--- a/naver-place-crawler/results_health/서초_PT.xlsx
+++ b/naver-place-crawler/results_health/서초_PT.xlsx
@@ -417,22 +417,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="46" customWidth="1" min="7" max="7"/>
+    <col width="39" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>고마워휘트니스 교대PT</t>
+          <t>헤이븐PT 교대점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>gmw1253@naver.com</t>
+          <t>studio_haven@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1455-1284</t>
+          <t>0507-1410-1595</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>서울특별시 서초구 서초중앙로 166 B1 고마워 휘트니스</t>
+          <t>서울특별시 서초구 서초중앙로28길 6 가정빌딩 4층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gmw1253/223435367519</t>
+          <t>https://blog.naver.com/studio_haven</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -617,17 +617,17 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>342</v>
+        <v>22</v>
       </c>
       <c r="Q2" t="n">
-        <v>1641</v>
+        <v>82</v>
       </c>
       <c r="R2" t="n">
-        <v>1983</v>
+        <v>104</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,51 +636,51 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>11875969</t>
+          <t>37157624</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/11875969</t>
+          <t>https://m.place.naver.com/place/37157624</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>씨엘필라테스 반포점</t>
+          <t>고마워휘트니스 교대PT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>clpilates9@naver.com</t>
+          <t>gmw1253@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1382-6396</t>
+          <t>0507-1455-1284</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>서울 서초구 서초중앙로 209 9층</t>
+          <t>서울특별시 서초구 서초중앙로 166 B1 고마워 휘트니스</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/clpilates9</t>
+          <t>https://blog.naver.com/gmw1253/223435367519</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -700,14 +700,10 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wfgvhue</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -719,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>115</v>
+        <v>342</v>
       </c>
       <c r="Q3" t="n">
-        <v>601</v>
+        <v>1641</v>
       </c>
       <c r="R3" t="n">
-        <v>716</v>
+        <v>1983</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -734,17 +730,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2014815734</t>
+          <t>11875969</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2014815734</t>
+          <t>https://m.place.naver.com/place/11875969</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -813,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1974</v>
+        <v>1975</v>
       </c>
       <c r="Q4" t="n">
         <v>1606</v>
       </c>
       <c r="R4" t="n">
-        <v>3580</v>
+        <v>3581</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -838,7 +834,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -932,7 +928,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1018,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1116,7 +1112,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1210,41 +1206,41 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>휴메이크휘트니스 강남점</t>
+          <t>MOVA PT&amp;PILATES</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>humake001@naver.com</t>
+          <t>agenda11301@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1432-0174</t>
+          <t>0507-1419-2072</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울특별시 서초구 강남대로 327 대륭서초타워 지하2층</t>
+          <t>서울특별시 서초구 잠원로4길 50 동관1동 3층 315-316호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/humakefitness_gn</t>
+          <t>https://www.instagram.com/mova_studio_</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1279,13 +1275,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1019</v>
+        <v>46</v>
       </c>
       <c r="Q9" t="n">
-        <v>1271</v>
+        <v>7</v>
       </c>
       <c r="R9" t="n">
-        <v>2290</v>
+        <v>53</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,51 +1290,51 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>20077206</t>
+          <t>2004778615</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20077206</t>
+          <t>https://m.place.naver.com/place/2004778615</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>리프레쉬클럽 PT 반포래미안점</t>
+          <t>휴메이크휘트니스 강남점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>refreshbanpo@naver.com</t>
+          <t>humake001@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1402-8731</t>
+          <t>0507-1432-0174</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울특별시 서초구 반포대로 287 래미안퍼스티지중심상가 3층 327호, 328호</t>
+          <t>서울특별시 서초구 강남대로 327 대륭서초타워 지하2층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/refreshbanpo</t>
+          <t>http://www.instagram.com/humakefitness_gn</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1353,7 +1349,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1373,13 +1369,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>302</v>
+        <v>1019</v>
       </c>
       <c r="Q10" t="n">
-        <v>353</v>
+        <v>1271</v>
       </c>
       <c r="R10" t="n">
-        <v>655</v>
+        <v>2290</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,51 +1384,51 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>20451191</t>
+          <t>20077206</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20451191</t>
+          <t>https://m.place.naver.com/place/20077206</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>휴메이크휘트니스 서초점</t>
+          <t>트리니티 PT Pilates LAB</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>humakesc@naver.com</t>
+          <t>trinity_pt@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1352-4800</t>
+          <t>0507-2097-3213</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울특별시 서초구 반포대로 34 로얄빌딩 지하1층 휴메이크휘트니스 서초점</t>
+          <t>서울특별시 서초구 서초대로48길 107 6층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/humakesc</t>
+          <t>https://blog.naver.com/trinity_pt</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1467,13 +1463,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>775</v>
+        <v>74</v>
       </c>
       <c r="Q11" t="n">
-        <v>1024</v>
+        <v>99</v>
       </c>
       <c r="R11" t="n">
-        <v>1799</v>
+        <v>173</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1482,17 +1478,205 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>32308075</t>
+          <t>1015744638</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/32308075</t>
+          <t>https://m.place.naver.com/place/1015744638</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>글로우짐 PT</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>glowgym_2021@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1479-8448</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>서울특별시 서초구 고무래로 32 지하1층</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/glowgym_2021</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>106</v>
+      </c>
+      <c r="R12" t="n">
+        <v>164</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>1745859115</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1745859115</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>크레이지독스짐</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>bodyartist7@naver.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0507-1314-7087</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>서울특별시 서초구 효령로31길 10 지하 1층</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/bodyartist7</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>789</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>400</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1189</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>1659233801</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1659233801</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/서초_PT.xlsx
+++ b/naver-place-crawler/results_health/서초_PT.xlsx
@@ -427,12 +427,12 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="39" customWidth="1" min="7" max="7"/>
-    <col width="45" customWidth="1" min="8" max="8"/>
+    <col width="43" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -653,34 +653,34 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>고마워휘트니스 교대PT</t>
+          <t>씨엘필라테스 반포점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>gmw1253@naver.com</t>
+          <t>clpilates9@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1455-1284</t>
+          <t>0507-1382-6396</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>서울특별시 서초구 서초중앙로 166 B1 고마워 휘트니스</t>
+          <t>서울 서초구 서초중앙로 209 9층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gmw1253/223435367519</t>
+          <t>https://blog.naver.com/clpilates9</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -700,10 +700,14 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wfgvhue</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -715,13 +719,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>342</v>
+        <v>115</v>
       </c>
       <c r="Q3" t="n">
-        <v>1641</v>
+        <v>602</v>
       </c>
       <c r="R3" t="n">
-        <v>1983</v>
+        <v>717</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,12 +734,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>11875969</t>
+          <t>2014815734</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/11875969</t>
+          <t>https://m.place.naver.com/place/2014815734</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -1213,34 +1217,34 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MOVA PT&amp;PILATES</t>
+          <t>휴메이크휘트니스 강남점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>agenda11301@naver.com</t>
+          <t>humake001@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1419-2072</t>
+          <t>0507-1432-0174</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울특별시 서초구 잠원로4길 50 동관1동 3층 315-316호</t>
+          <t>서울특별시 서초구 강남대로 327 대륭서초타워 지하2층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/mova_studio_</t>
+          <t>http://www.instagram.com/humakefitness_gn</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1275,13 +1279,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>46</v>
+        <v>1019</v>
       </c>
       <c r="Q9" t="n">
-        <v>7</v>
+        <v>1271</v>
       </c>
       <c r="R9" t="n">
-        <v>53</v>
+        <v>2290</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1290,12 +1294,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2004778615</t>
+          <t>20077206</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2004778615</t>
+          <t>https://m.place.naver.com/place/20077206</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1307,34 +1311,34 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>휴메이크휘트니스 강남점</t>
+          <t>트리니티 PT Pilates LAB</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>humake001@naver.com</t>
+          <t>trinity_pt@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1432-0174</t>
+          <t>0507-2097-3213</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울특별시 서초구 강남대로 327 대륭서초타워 지하2층</t>
+          <t>서울특별시 서초구 서초대로48길 107 6층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/humakefitness_gn</t>
+          <t>https://blog.naver.com/trinity_pt</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1349,7 +1353,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1369,13 +1373,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1019</v>
+        <v>74</v>
       </c>
       <c r="Q10" t="n">
-        <v>1271</v>
+        <v>99</v>
       </c>
       <c r="R10" t="n">
-        <v>2290</v>
+        <v>173</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1384,12 +1388,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>20077206</t>
+          <t>1015744638</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20077206</t>
+          <t>https://m.place.naver.com/place/1015744638</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1406,29 +1410,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>트리니티 PT Pilates LAB</t>
+          <t>글로우짐 PT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>trinity_pt@naver.com</t>
+          <t>glowgym_2021@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-2097-3213</t>
+          <t>0507-1479-8448</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울특별시 서초구 서초대로48길 107 6층</t>
+          <t>서울특별시 서초구 고무래로 32 지하1층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/trinity_pt</t>
+          <t>https://blog.naver.com/glowgym_2021</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1463,13 +1467,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="Q11" t="n">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="R11" t="n">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1478,12 +1482,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1015744638</t>
+          <t>1745859115</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1015744638</t>
+          <t>https://m.place.naver.com/place/1745859115</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1495,34 +1499,34 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>글로우짐 PT</t>
+          <t>크레이지독스짐</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>glowgym_2021@naver.com</t>
+          <t>bodyartist7@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1479-8448</t>
+          <t>0507-1314-7087</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>서울특별시 서초구 고무래로 32 지하1층</t>
+          <t>서울특별시 서초구 효령로31길 10 지하 1층</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/glowgym_2021</t>
+          <t>https://blog.naver.com/bodyartist7</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1557,13 +1561,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>58</v>
+        <v>789</v>
       </c>
       <c r="Q12" t="n">
-        <v>106</v>
+        <v>400</v>
       </c>
       <c r="R12" t="n">
-        <v>164</v>
+        <v>1189</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1572,12 +1576,12 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1745859115</t>
+          <t>1659233801</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1745859115</t>
+          <t>https://m.place.naver.com/place/1659233801</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1594,29 +1598,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>크레이지독스짐</t>
+          <t>휘트니스피플 우먼 논현점</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>bodyartist7@naver.com</t>
+          <t>fpeoplew1@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0507-1314-7087</t>
+          <t>02-511-3912</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>서울특별시 서초구 효령로31길 10 지하 1층</t>
+          <t>서울특별시 서초구 강남대로 557 지하2층</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bodyartist7</t>
+          <t>https://blog.naver.com/fpeoplew1</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1651,13 +1655,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>789</v>
+        <v>994</v>
       </c>
       <c r="Q13" t="n">
-        <v>400</v>
+        <v>1232</v>
       </c>
       <c r="R13" t="n">
-        <v>1189</v>
+        <v>2226</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1666,12 +1670,12 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1659233801</t>
+          <t>1334450349</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1659233801</t>
+          <t>https://m.place.naver.com/place/1334450349</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
